--- a/测试集/泛用性验收_v3/W3/W3_拆分_安全管理部.xlsx
+++ b/测试集/泛用性验收_v3/W3/W3_拆分_安全管理部.xlsx
@@ -44,7 +44,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -66,19 +66,74 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -440,8 +495,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -456,29 +521,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>责任单位</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>完成时限</t>
-        </is>
-      </c>
+          <t>基本信息</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="n"/>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>计划数</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>完成数</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>完成率</t>
-        </is>
-      </c>
+          <t>进度</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="2" t="n"/>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
@@ -486,46 +539,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>季度报表汇总</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>安全管理部</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24</v>
-      </c>
-      <c r="G2">
-        <f>F2/E2</f>
-        <v/>
-      </c>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>责任单位</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>完成时限</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>计划数</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>完成数</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A008</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>新员工入职办理</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -535,21 +586,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <f>F3/E3</f>
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A008</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>新员工入职办理</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>安全管理部</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G4">
+        <f>F4/E4</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G3:G4">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/测试集/泛用性验收_v3/W3/W3_拆分_安全管理部.xlsx
+++ b/测试集/泛用性验收_v3/W3/W3_拆分_安全管理部.xlsx
@@ -495,149 +495,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>任务名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>基本信息</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>进度</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>任务执行情况统计表</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>责任单位</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>完成时限</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>计划数</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>完成数</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>完成率</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>填报说明：请各单位如实填报执行进度。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>季度报表汇总</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>安全管理部</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F3" t="n">
-        <v>24</v>
-      </c>
-      <c r="G3">
-        <f>F3/E3</f>
-        <v/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>任务名称</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>基本信息</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>进度</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr"/>
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>责任单位</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>完成时限</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>计划数</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>完成数</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>季度报表汇总</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>安全管理部</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <f>F5/E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A008</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>新员工入职办理</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>安全管理部</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" t="n">
         <v>80</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F6" t="n">
         <v>80</v>
       </c>
-      <c r="G4">
-        <f>F4/E4</f>
+      <c r="G6">
+        <f>F6/E6</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:G1"/>
+  <mergeCells count="4">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G4">
+  <conditionalFormatting sqref="G5:G6">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0.5</formula>
     </cfRule>
